--- a/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
+++ b/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
@@ -1831,10 +1831,10 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2024-10-16 18:12:09</t>
-  </si>
-  <si>
-    <t>KiCost® v1.1.18 + KiBot v1.8.2</t>
+    <t>2024-11-01 00:44:16</t>
+  </si>
+  <si>
+    <t>KiCost® v1.1.18 + KiBot v1.8.3</t>
   </si>
   <si>
     <t>Columns colors</t>

--- a/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
+++ b/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
@@ -1783,7 +1783,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>8.0.5-8.0.5-0~ubuntu24.04.1</t>
+    <t>8.0.6-8.0.6-0~ubuntu24.04.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -1831,7 +1831,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2024-11-01 00:44:16</t>
+    <t>2024-11-12 19:29:53</t>
   </si>
   <si>
     <t>KiCost® v1.1.18 + KiBot v1.8.3</t>

--- a/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
+++ b/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
@@ -1831,7 +1831,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2024-11-12 19:29:53</t>
+    <t>2024-11-13 13:57:42</t>
   </si>
   <si>
     <t>KiCost® v1.1.18 + KiBot v1.8.3</t>

--- a/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
+++ b/amulet_controller/Generated/Manufacturing/Assembly/amulet_controller-bom.xlsx
@@ -1831,7 +1831,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2024-11-13 13:57:42</t>
+    <t>2024-11-14 23:04:15</t>
   </si>
   <si>
     <t>KiCost® v1.1.18 + KiBot v1.8.3</t>
@@ -2004,7 +2004,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF009879"/>
+        <fgColor rgb="FF0E4E8E"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
